--- a/artfynd/A 61865-2023 artfynd.xlsx
+++ b/artfynd/A 61865-2023 artfynd.xlsx
@@ -1319,11 +1319,11 @@
         <v>116344766</v>
       </c>
       <c r="B8" t="n">
-        <v>56493</v>
+        <v>56596</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2701,11 +2701,11 @@
         <v>116345565</v>
       </c>
       <c r="B21" t="n">
-        <v>56490</v>
+        <v>56593</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4507,11 +4507,11 @@
         <v>116345511</v>
       </c>
       <c r="B38" t="n">
-        <v>56490</v>
+        <v>56593</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">

--- a/artfynd/A 61865-2023 artfynd.xlsx
+++ b/artfynd/A 61865-2023 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>116344766</v>
       </c>
       <c r="B8" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>116345565</v>
       </c>
       <c r="B21" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>116345511</v>
       </c>
       <c r="B38" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 61865-2023 artfynd.xlsx
+++ b/artfynd/A 61865-2023 artfynd.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61865-2023 artfynd.xlsx
+++ b/artfynd/A 61865-2023 artfynd.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
